--- a/data/sistema/procesada/banca/banca_unida.xlsx
+++ b/data/sistema/procesada/banca/banca_unida.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1086"/>
+  <dimension ref="A1:F1123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28639,7 +28639,7 @@
     <row r="1086">
       <c r="A1086" t="inlineStr">
         <is>
-          <t>fa72c0db6e60053e17c5d61b275ee789</t>
+          <t>05b555851be7e2538bbc6d26d5459ac8</t>
         </is>
       </c>
       <c r="B1086" s="1" t="n">
@@ -28647,7 +28647,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>TRANSFERENCIA INTERBANCARIA A FRUTAS Y LEGUMBRES ASIRI</t>
+          <t>TRANSFERENCIA INTERBANCARIA ENVIADA</t>
         </is>
       </c>
       <c r="D1086" t="n">
@@ -28660,6 +28660,968 @@
       </c>
       <c r="F1086" t="n">
         <v>483.38</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>395c31e5a3b0f6df93d85d49b2d97225</t>
+        </is>
+      </c>
+      <c r="B1087" s="1" t="n">
+        <v>46216.10763888889</v>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A GUEVARA OLMEDO MATEO NICOLAS</t>
+        </is>
+      </c>
+      <c r="D1087" t="n">
+        <v>-25.05</v>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1087" t="n">
+        <v>458.33</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>9f46d7db21c0402317e34634b5c7b4ef</t>
+        </is>
+      </c>
+      <c r="B1088" s="1" t="n">
+        <v>46216.20277777778</v>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICAIZA ERAZO SEBASTIAN MATEO</t>
+        </is>
+      </c>
+      <c r="D1088" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1088" t="n">
+        <v>448.33</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>b71c70c29f074d03f79c9f97ab76795f</t>
+        </is>
+      </c>
+      <c r="B1089" s="1" t="n">
+        <v>46216.84722222222</v>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A OÑA LEDESMA PATRICIO NICOLAS</t>
+        </is>
+      </c>
+      <c r="D1089" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1089" t="n">
+        <v>443.58</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>ec0729c7124161f8cc110ea85323f458</t>
+        </is>
+      </c>
+      <c r="B1090" s="1" t="n">
+        <v>46216.84930555556</v>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A OÑA LEDESMA PATRICIO NICOLAS</t>
+        </is>
+      </c>
+      <c r="D1090" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1090" t="n">
+        <v>443.23</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>4f85992804dac908d035a4f606ac3c53</t>
+        </is>
+      </c>
+      <c r="B1091" s="1" t="n">
+        <v>46216.94444444445</v>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>TRANSF. DEUNA A XIMENA PATRICIA HARO ORTEGA</t>
+        </is>
+      </c>
+      <c r="D1091" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1091" t="n">
+        <v>435.23</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>3f206b7f2123536d4b2d9ff30c6e6acc</t>
+        </is>
+      </c>
+      <c r="B1092" s="1" t="n">
+        <v>46216.68125</v>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A VERKADE MONTIEL DOMINIQUE LOURDES</t>
+        </is>
+      </c>
+      <c r="D1092" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1092" t="n">
+        <v>432.88</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>701cd89b2674695bb1966419a2ac5cdb</t>
+        </is>
+      </c>
+      <c r="B1093" s="1" t="n">
+        <v>46219.41944444444</v>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A PANILUISA CHICAIZA EDISON ORLANDO</t>
+        </is>
+      </c>
+      <c r="D1093" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1093" t="n">
+        <v>431.48</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>6d46101a9acb374eef18f0ad8409c93d</t>
+        </is>
+      </c>
+      <c r="B1094" s="1" t="n">
+        <v>46219.58958333333</v>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICHANDA LOOR BETTY FABIOLA</t>
+        </is>
+      </c>
+      <c r="D1094" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1094" t="n">
+        <v>427.48</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>0db6e9f6800cca031c5072ef1e2701c4</t>
+        </is>
+      </c>
+      <c r="B1095" s="1" t="n">
+        <v>46220.60902777778</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICHANDA LOOR BETTY FABIOLA</t>
+        </is>
+      </c>
+      <c r="D1095" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1095" t="n">
+        <v>423.48</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>ffd128739a7aebb21c8e21ab5c33cc49</t>
+        </is>
+      </c>
+      <c r="B1096" s="1" t="n">
+        <v>46223.84236111111</v>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A PANILUISA CHICAIZA EDISON ORLANDO</t>
+        </is>
+      </c>
+      <c r="D1096" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1096" t="n">
+        <v>421.28</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>800d3b0eee05b81e3e8a0e32ba33c99e</t>
+        </is>
+      </c>
+      <c r="B1097" s="1" t="n">
+        <v>46223.57083333333</v>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A IDROVO ZAMBRANO NATALIA ALEXANDRA</t>
+        </is>
+      </c>
+      <c r="D1097" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1097" t="n">
+        <v>416.28</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>a496491a4002175b773e9f468de83c52</t>
+        </is>
+      </c>
+      <c r="B1098" s="1" t="n">
+        <v>46223.88263888889</v>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>TRANSF. DEUNA A CARMEN OLIMPIA AULES CHINCHERO</t>
+        </is>
+      </c>
+      <c r="D1098" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1098" t="n">
+        <v>412.28</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>da884c63941c5e899dec1b6689ac60fc</t>
+        </is>
+      </c>
+      <c r="B1099" s="1" t="n">
+        <v>46223.48472222222</v>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE ARCINIEGA BASANTES PAULINA MARIA</t>
+        </is>
+      </c>
+      <c r="D1099" t="n">
+        <v>237.31</v>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1099" t="n">
+        <v>649.59</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>7c421bdbd1a60bb675917f2d33d7b151</t>
+        </is>
+      </c>
+      <c r="B1100" s="1" t="n">
+        <v>46223.61111111111</v>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICHANDA LOOR BETTY FABIOLA</t>
+        </is>
+      </c>
+      <c r="D1100" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1100" t="n">
+        <v>645.59</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>c3388deb8ae628005adca96b848c7d9d</t>
+        </is>
+      </c>
+      <c r="B1101" s="1" t="n">
+        <v>46224.39791666667</v>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>PAGO TARJETA:  2230670000895647</t>
+        </is>
+      </c>
+      <c r="D1101" t="n">
+        <v>-25</v>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1101" t="n">
+        <v>620.59</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>30206d562bd2d6976d44ef215f4f98fe</t>
+        </is>
+      </c>
+      <c r="B1102" s="1" t="n">
+        <v>46224.58819444444</v>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICHANDA LOOR BETTY FABIOLA</t>
+        </is>
+      </c>
+      <c r="D1102" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1102" t="n">
+        <v>616.59</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>58aa2d4bb450f50895d0120ed61440ee</t>
+        </is>
+      </c>
+      <c r="B1103" s="1" t="n">
+        <v>46225.60138888889</v>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICHANDA LOOR BETTY FABIOLA</t>
+        </is>
+      </c>
+      <c r="D1103" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1103" t="n">
+        <v>608.59</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>40813715a0c46f49b8b3eb183fcb29a6</t>
+        </is>
+      </c>
+      <c r="B1104" s="1" t="n">
+        <v>46225.87777777778</v>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>TRANSF. DEUNA A XIMENA PATRICIA HARO ORTEGA</t>
+        </is>
+      </c>
+      <c r="D1104" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1104" t="n">
+        <v>603.09</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>4bcdddfc88b214eb5427b7061f255653</t>
+        </is>
+      </c>
+      <c r="B1105" s="1" t="n">
+        <v>46225.93472222222</v>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>TRANSF. DEUNA A CHRISTIAN ROBERTO FALCONI ARMAS</t>
+        </is>
+      </c>
+      <c r="D1105" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1105" t="n">
+        <v>595.59</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>b7334404131d5131176a5517e98d8f5c</t>
+        </is>
+      </c>
+      <c r="B1106" s="1" t="n">
+        <v>46226.61319444444</v>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICHANDA LOOR BETTY FABIOLA</t>
+        </is>
+      </c>
+      <c r="D1106" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1106" t="n">
+        <v>587.59</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>e2ced640c542b0a06ef5010d5a702d35</t>
+        </is>
+      </c>
+      <c r="B1107" s="1" t="n">
+        <v>46230.34444444445</v>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>CANCELACION PLAZO FIJO</t>
+        </is>
+      </c>
+      <c r="D1107" t="n">
+        <v>27000</v>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1107" t="n">
+        <v>27587.59</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>eb4202115378e3b592b94ec9542279c5</t>
+        </is>
+      </c>
+      <c r="B1108" s="1" t="n">
+        <v>46230.34444444445</v>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>REGULARIZACIÓN DE TRANSACCIÓN</t>
+        </is>
+      </c>
+      <c r="D1108" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1108" t="n">
+        <v>27657.19</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>8998f5c9c873d94949f021f224ab7106</t>
+        </is>
+      </c>
+      <c r="B1109" s="1" t="n">
+        <v>46230.34444444445</v>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>RETENCION RENDIMIENTO FINANCIERO</t>
+        </is>
+      </c>
+      <c r="D1109" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1109" t="n">
+        <v>27655.1</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>6d16e9a94eef507b24ab8cfb863dec1c</t>
+        </is>
+      </c>
+      <c r="B1110" s="1" t="n">
+        <v>46231.60694444444</v>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICHANDA LOOR BETTY FABIOLA</t>
+        </is>
+      </c>
+      <c r="D1110" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1110" t="n">
+        <v>27651.1</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2f86c7616c75f7b65b7053c71e5633d3</t>
+        </is>
+      </c>
+      <c r="B1111" s="1" t="n">
+        <v>46232.58333333334</v>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICHANDA LOOR BETTY FABIOLA</t>
+        </is>
+      </c>
+      <c r="D1111" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1111" t="n">
+        <v>27647.6</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>ecd57e1d8c81e9d7f057c6a89b772e5f</t>
+        </is>
+      </c>
+      <c r="B1112" s="1" t="n">
+        <v>46234.64791666667</v>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A VERKADE MONTIEL DOMINIQUE LOURDES</t>
+        </is>
+      </c>
+      <c r="D1112" t="n">
+        <v>-7.32</v>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1112" t="n">
+        <v>27640.28</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>e86378bc16cff0b436a93c05831fefa7</t>
+        </is>
+      </c>
+      <c r="B1113" s="1" t="n">
+        <v>46234.06736111111</v>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>INTERÉS ACREDITADO EN SU CUENTA</t>
+        </is>
+      </c>
+      <c r="D1113" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1113" t="n">
+        <v>27640.3</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>aa31b26522da7bbe6f76565af9627cf3</t>
+        </is>
+      </c>
+      <c r="B1114" s="1" t="n">
+        <v>46237.16111111111</v>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>TRANSF. DEUNA A MATEO ISRAEL CAGUAS YUNGAN</t>
+        </is>
+      </c>
+      <c r="D1114" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1114" t="n">
+        <v>27637.3</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>60506149eb888af307d9e4dcbafda758</t>
+        </is>
+      </c>
+      <c r="B1115" s="1" t="n">
+        <v>46237.85138888889</v>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>TRANSF. DEUNA A ROSA ELIZABETH JIMENEZ ARELLANO</t>
+        </is>
+      </c>
+      <c r="D1115" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1115" t="n">
+        <v>27632.5</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>fdaac36f3c08c457762512ef12cf8c5e</t>
+        </is>
+      </c>
+      <c r="B1116" s="1" t="n">
+        <v>46237.90694444445</v>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>TRANSF. INTERBANCARIA DE DANIEL ORLANDO GALLARDO PINEDA</t>
+        </is>
+      </c>
+      <c r="D1116" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1116" t="n">
+        <v>27642.5</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>f497162c3840d36245146ea55169f13d</t>
+        </is>
+      </c>
+      <c r="B1117" s="1" t="n">
+        <v>46237.90694444445</v>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE FELIPE JOSHUA SOLORZANO FLORES</t>
+        </is>
+      </c>
+      <c r="D1117" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1117" t="n">
+        <v>27652.5</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>a980dc2e59b23aac609a49a9dce00478</t>
+        </is>
+      </c>
+      <c r="B1118" s="1" t="n">
+        <v>46237.90694444445</v>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE JUAN JOSE PARDO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="D1118" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1118" t="n">
+        <v>27662.5</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>51c132f230bb357db038046da3788190</t>
+        </is>
+      </c>
+      <c r="B1119" s="1" t="n">
+        <v>46237.91319444445</v>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE MARCELO ANDRES AGUILAR CIFUENTES</t>
+        </is>
+      </c>
+      <c r="D1119" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1119" t="n">
+        <v>27676.5</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>c963773b50f0c15ab15da7cc398478b8</t>
+        </is>
+      </c>
+      <c r="B1120" s="1" t="n">
+        <v>46237.91319444445</v>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>TRANSF. INTERBANCARIA DE DANIEL ORLANDO GALLARDO PINEDA</t>
+        </is>
+      </c>
+      <c r="D1120" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1120" t="n">
+        <v>27680.5</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>dc60ef329307d5b9ad25d139d292abfa</t>
+        </is>
+      </c>
+      <c r="B1121" s="1" t="n">
+        <v>46237.91319444445</v>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE FELIPE JOSHUA SOLORZANO FLORES</t>
+        </is>
+      </c>
+      <c r="D1121" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1121" t="n">
+        <v>27688.5</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>e31365b8d5f14c2b4c8b322190e274de</t>
+        </is>
+      </c>
+      <c r="B1122" s="1" t="n">
+        <v>46237.43402777778</v>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A TOAPANTA TENORIO ERNESTO LEONIDAS</t>
+        </is>
+      </c>
+      <c r="D1122" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1122" t="n">
+        <v>27684.5</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>bfc29c9ca7bf0b9f6f8a72e690c95b8c</t>
+        </is>
+      </c>
+      <c r="B1123" s="1" t="n">
+        <v>46237.56736111111</v>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>TRANSF. DEUNA A MULTICINES S A MULTICINES</t>
+        </is>
+      </c>
+      <c r="D1123" t="n">
+        <v>-21.99</v>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1123" t="n">
+        <v>27662.51</v>
       </c>
     </row>
   </sheetData>

--- a/data/sistema/procesada/banca/banca_unida.xlsx
+++ b/data/sistema/procesada/banca/banca_unida.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1123"/>
+  <dimension ref="A1:F1164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29624,6 +29624,1072 @@
         <v>27662.51</v>
       </c>
     </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>9635e4328061fc64bc185b1417345f76</t>
+        </is>
+      </c>
+      <c r="B1124" s="1" t="n">
+        <v>46239.59791666667</v>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICHANDA LOOR BETTY FABIOLA</t>
+        </is>
+      </c>
+      <c r="D1124" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1124" t="n">
+        <v>27659.01</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>fd8346a993278ad5698e3bb72d6bf2a0</t>
+        </is>
+      </c>
+      <c r="B1125" s="1" t="n">
+        <v>46241.52013888889</v>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERNET</t>
+        </is>
+      </c>
+      <c r="D1125" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1125" t="n">
+        <v>27649.01</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>4765fce891a5aee6ca867120020387b2</t>
+        </is>
+      </c>
+      <c r="B1126" s="1" t="n">
+        <v>46241.59097222222</v>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERNET</t>
+        </is>
+      </c>
+      <c r="D1126" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1126" t="n">
+        <v>27645.51</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>e4592d9a17a01eacd62cb27eb7948bf8</t>
+        </is>
+      </c>
+      <c r="B1127" s="1" t="n">
+        <v>46241.59166666667</v>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERNET</t>
+        </is>
+      </c>
+      <c r="D1127" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1127" t="n">
+        <v>27645.01</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>d45078e32dc940d832b99c69c7922253</t>
+        </is>
+      </c>
+      <c r="B1128" s="1" t="n">
+        <v>46241.76319444444</v>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERNET</t>
+        </is>
+      </c>
+      <c r="D1128" t="n">
+        <v>-27.61</v>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1128" t="n">
+        <v>27617.4</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>851fffbf9e91a2a6197524858bcdff25</t>
+        </is>
+      </c>
+      <c r="B1129" s="1" t="n">
+        <v>46245.58194444444</v>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERNET</t>
+        </is>
+      </c>
+      <c r="D1129" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1129" t="n">
+        <v>27613.4</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>b4ee964a27ae21b9be3ab983eb009631</t>
+        </is>
+      </c>
+      <c r="B1130" s="1" t="n">
+        <v>46245.58263888889</v>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERNET</t>
+        </is>
+      </c>
+      <c r="D1130" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1130" t="n">
+        <v>27611.4</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>13592fadfd5d92dbd1f1cf619fea46cd</t>
+        </is>
+      </c>
+      <c r="B1131" s="1" t="n">
+        <v>46245.78680555556</v>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERNET</t>
+        </is>
+      </c>
+      <c r="D1131" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1131" t="n">
+        <v>27609.57</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2c2fa189216602fd670dd60d3219e339</t>
+        </is>
+      </c>
+      <c r="B1132" s="1" t="n">
+        <v>46246.58263888889</v>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A CHICHANDA LOOR BETTY FABIOLA</t>
+        </is>
+      </c>
+      <c r="D1132" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1132" t="n">
+        <v>27605.57</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>8cf822e91b5dc785e89ba2641b4ddaaf</t>
+        </is>
+      </c>
+      <c r="B1133" s="1" t="n">
+        <v>46248.08819444444</v>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>17056306-MASTERCARD BP  -8E-223067000075</t>
+        </is>
+      </c>
+      <c r="D1133" t="n">
+        <v>-496.85</v>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1133" t="n">
+        <v>27108.72</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>9fa9f58b9d516761b1db07221dc03c3e</t>
+        </is>
+      </c>
+      <c r="B1134" s="1" t="n">
+        <v>46248.53194444445</v>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERNET</t>
+        </is>
+      </c>
+      <c r="D1134" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1134" t="n">
+        <v>27105.22</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>6b5818f01881443bc9e1b00cb56571e6</t>
+        </is>
+      </c>
+      <c r="B1135" s="1" t="n">
+        <v>46251.58125</v>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A DAVILA IZQUIERDO MARIA DE LOURDES</t>
+        </is>
+      </c>
+      <c r="D1135" t="n">
+        <v>-8</v>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1135" t="n">
+        <v>27097.22</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>d02c00c9d87e4d27ccef83cdda6449a9</t>
+        </is>
+      </c>
+      <c r="B1136" s="1" t="n">
+        <v>46251.38888888889</v>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE CHICAIZA NAVARRETE ALEJANDRO MANUEL</t>
+        </is>
+      </c>
+      <c r="D1136" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1136" t="n">
+        <v>27103.22</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>9ee0259961617e323767d25ecbbd6838</t>
+        </is>
+      </c>
+      <c r="B1137" s="1" t="n">
+        <v>46251.58680555555</v>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A QUIÑONEZ ANGULO LIGIA NELLY</t>
+        </is>
+      </c>
+      <c r="D1137" t="n">
+        <v>-30</v>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1137" t="n">
+        <v>27073.22</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>883e7e3a881164b2888ace7158180ab5</t>
+        </is>
+      </c>
+      <c r="B1138" s="1" t="n">
+        <v>46251.53055555555</v>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A QUIÑONEZ ANGULO NANCY MIRELLA</t>
+        </is>
+      </c>
+      <c r="D1138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1138" t="n">
+        <v>27072.22</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>4e5d8a38302242c5aa96c9a277cc1e62</t>
+        </is>
+      </c>
+      <c r="B1139" s="1" t="n">
+        <v>46251.7375</v>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERBANCARIA ENVIADA</t>
+        </is>
+      </c>
+      <c r="D1139" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1139" t="n">
+        <v>27065.87</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>57dd25d008415df3ffc69431fe5c6029</t>
+        </is>
+      </c>
+      <c r="B1140" s="1" t="n">
+        <v>46254.69861111111</v>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D1140" t="n">
+        <v>600</v>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1140" t="n">
+        <v>27665.87</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>24dda2c74b3733fee80079964236b3fd</t>
+        </is>
+      </c>
+      <c r="B1141" s="1" t="n">
+        <v>46254.76527777778</v>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERBANCARIA ENVIADA</t>
+        </is>
+      </c>
+      <c r="D1141" t="n">
+        <v>-21.73</v>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1141" t="n">
+        <v>27644.14</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>80b1ece640c46d73698b91d70f88fcf7</t>
+        </is>
+      </c>
+      <c r="B1142" s="1" t="n">
+        <v>46254.79305555556</v>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A PAZMIÑO VALLEJO NORMA ISABEL</t>
+        </is>
+      </c>
+      <c r="D1142" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1142" t="n">
+        <v>27632.64</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>4e662766a5d39048c73d87f8c391125b</t>
+        </is>
+      </c>
+      <c r="B1143" s="1" t="n">
+        <v>46254.80625</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERBANCARIA ENVIADA</t>
+        </is>
+      </c>
+      <c r="D1143" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1143" t="n">
+        <v>27627.39</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>34f5e2da39bc4748a90f70f7a19495f2</t>
+        </is>
+      </c>
+      <c r="B1144" s="1" t="n">
+        <v>46254.80694444444</v>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA INTERBANCARIA ENVIADA</t>
+        </is>
+      </c>
+      <c r="D1144" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1144" t="n">
+        <v>27626.64</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>ebc9ab0f952b922bd3e9eb2b56f12acb</t>
+        </is>
+      </c>
+      <c r="B1145" s="1" t="n">
+        <v>46255.89444444444</v>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A VERKADE MONTIEL DOMINIQUE LOURDES</t>
+        </is>
+      </c>
+      <c r="D1145" t="n">
+        <v>-496.83</v>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1145" t="n">
+        <v>27129.81</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>99178caa884b1e3e643aada7b03755ed</t>
+        </is>
+      </c>
+      <c r="B1146" s="1" t="n">
+        <v>46255.89583333334</v>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A MEDINA AYALA VIOLETA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="D1146" t="n">
+        <v>-120.04</v>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1146" t="n">
+        <v>27009.77</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>eca706569c3701a2c829e41b423e8fb8</t>
+        </is>
+      </c>
+      <c r="B1147" s="1" t="n">
+        <v>46258.425</v>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>COMISION TRANSFERENCIA INTERBANCARIA ENVIADA</t>
+        </is>
+      </c>
+      <c r="D1147" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1147" t="n">
+        <v>27009.41</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>8afd8a9ff7c7e5bd43d8e182a8017475</t>
+        </is>
+      </c>
+      <c r="B1148" s="1" t="n">
+        <v>46258.425</v>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>IVA COBRADO</t>
+        </is>
+      </c>
+      <c r="D1148" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1148" t="n">
+        <v>27009.36</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>a58c03ee58fd01d5aac381b57eb1488c</t>
+        </is>
+      </c>
+      <c r="B1149" s="1" t="n">
+        <v>46258.425</v>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>TRANSF. INTERBANCARIA A ARCENTALES ARCINIEGA ANDRE SEBASTIA</t>
+        </is>
+      </c>
+      <c r="D1149" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1149" t="n">
+        <v>26999.36</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>9305451e69ce9ced56b8b8893c3dad5d</t>
+        </is>
+      </c>
+      <c r="B1150" s="1" t="n">
+        <v>46258.73194444444</v>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>TRANSF. DEUNA A HERNAN DARIO RAMOS VILLARREAL</t>
+        </is>
+      </c>
+      <c r="D1150" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1150" t="n">
+        <v>26989.36</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>ee99f8b025888c58d4a7c7307e164280</t>
+        </is>
+      </c>
+      <c r="B1151" s="1" t="n">
+        <v>46258.89236111111</v>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE VERKADE MONTIEL DOMINIQUE LOURDES</t>
+        </is>
+      </c>
+      <c r="D1151" t="n">
+        <v>208.67</v>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1151" t="n">
+        <v>27198.03</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>1e1665cdcab2c990c8692d58173811d7</t>
+        </is>
+      </c>
+      <c r="B1152" s="1" t="n">
+        <v>46258.38541666666</v>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>CERTIFICADO DE DEPOSITO</t>
+        </is>
+      </c>
+      <c r="D1152" t="n">
+        <v>-26000</v>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1152" t="n">
+        <v>1198.03</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>676d32e314370f76b33d6daae302efd3</t>
+        </is>
+      </c>
+      <c r="B1153" s="1" t="n">
+        <v>46258.39236111111</v>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE ARCENTALES ARCINIEGA ARIANNA NICOLE</t>
+        </is>
+      </c>
+      <c r="D1153" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1153" t="n">
+        <v>1298.03</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>284202fd538d08c3cc3ee9b47506ea0c</t>
+        </is>
+      </c>
+      <c r="B1154" s="1" t="n">
+        <v>46258.7</v>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE VERKADE MONTIEL DOMINIQUE LOURDES</t>
+        </is>
+      </c>
+      <c r="D1154" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1154" t="n">
+        <v>1313.09</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2cc31b5d1f1d9c9eb529d9497a11cf6e</t>
+        </is>
+      </c>
+      <c r="B1155" s="1" t="n">
+        <v>46259.60694444444</v>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE VERKADE MONTIEL DOMINIQUE LOURDES</t>
+        </is>
+      </c>
+      <c r="D1155" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1155" t="n">
+        <v>1314.71</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>479a94a4d9cf8de8a24f7bf19621e723</t>
+        </is>
+      </c>
+      <c r="B1156" s="1" t="n">
+        <v>46259.60763888889</v>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE MEDINA AYALA VIOLETA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="D1156" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1156" t="n">
+        <v>1324.06</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>7d2d0c5cacc66c51064a7760d11d2b93</t>
+        </is>
+      </c>
+      <c r="B1157" s="1" t="n">
+        <v>46259.79513888889</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A MEDINA AYALA VIOLETA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="D1157" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1157" t="n">
+        <v>1321.24</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>fca4e700c0ffef8913831c95b05f6d87</t>
+        </is>
+      </c>
+      <c r="B1158" s="1" t="n">
+        <v>46260.69583333333</v>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE MEDINA AYALA VIOLETA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="D1158" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1158" t="n">
+        <v>1370.92</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>0502398541604ed9773fb6f697442978</t>
+        </is>
+      </c>
+      <c r="B1159" s="1" t="n">
+        <v>46262.76944444444</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE MEDINA AYALA VIOLETA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="D1159" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1159" t="n">
+        <v>1422.56</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>ab868890b556b432049dca857e64c98b</t>
+        </is>
+      </c>
+      <c r="B1160" s="1" t="n">
+        <v>46262.77222222222</v>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE VERKADE MONTIEL DOMINIQUE LOURDES</t>
+        </is>
+      </c>
+      <c r="D1160" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1160" t="n">
+        <v>1466.43</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>5e8fd2a9be9399cc70dabf2b51d62f4c</t>
+        </is>
+      </c>
+      <c r="B1161" s="1" t="n">
+        <v>46262.77291666667</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE MEDINA AYALA VIOLETA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="D1161" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1161" t="n">
+        <v>1472.65</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>0f3dd315c4d8bcb1a81f561e3d4bec93</t>
+        </is>
+      </c>
+      <c r="B1162" s="1" t="n">
+        <v>46262.775</v>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA DE MEDINA AYALA VIOLETA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="D1162" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1162" t="n">
+        <v>1522.33</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>c1c3570ba3722857d5d5862530343218</t>
+        </is>
+      </c>
+      <c r="B1163" s="1" t="n">
+        <v>46265.03125</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>INTERES A SU FAVOR</t>
+        </is>
+      </c>
+      <c r="D1163" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1163" t="n">
+        <v>1522.49</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>1afa6fa8c14f7948bdbc77263f6881f4</t>
+        </is>
+      </c>
+      <c r="B1164" s="1" t="n">
+        <v>46267.14375</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>TRANSF. DIRECTA A MEDINA AYALA VIOLETA ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="D1164" t="n">
+        <v>-28.44</v>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>BANCO</t>
+        </is>
+      </c>
+      <c r="F1164" t="n">
+        <v>1494.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
